--- a/Media_Alunos.escola.xlsx
+++ b/Media_Alunos.escola.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,6 +716,46 @@
       </c>
       <c r="L7" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
